--- a/i_test/test_D3_coorte_con_caratterizzazione/med_RENDIS_Alg1_1.xlsx
+++ b/i_test/test_D3_coorte_con_caratterizzazione/med_RENDIS_Alg1_1.xlsx
@@ -22,10 +22,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
   <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">datasped</t>
+    <t xml:space="preserve">ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DATE</t>
   </si>
   <si>
     <t xml:space="preserve">P01</t>
@@ -123,12 +123,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -221,26 +225,26 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="2" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="2" t="n">
         <v>20</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="2" t="n">
         <v>30</v>
       </c>
     </row>
